--- a/Projeto/Dashboard.xlsx
+++ b/Projeto/Dashboard.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="612" documentId="11_BA59E1DD40FA2FA242A7DDFB1F5ED628BAF978EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC097AE4-6D50-4F30-9CC2-B8EBF6CC1214}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="11_BA59E1DD40FA2FA242A7DDFB1F5ED628BAF978EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2ED2192-2458-43EC-86D9-92FFA3E28A23}"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="132" windowWidth="22932" windowHeight="9240" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="96" yWindow="132" windowWidth="22932" windowHeight="9240" firstSheet="8" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KPIs" sheetId="2" state="hidden" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7763" uniqueCount="3721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7769" uniqueCount="3727">
   <si>
     <t>Indicador</t>
   </si>
@@ -11192,16 +11192,34 @@
     <t>Frequência e gravidade dos atrasos nas entregas</t>
   </si>
   <si>
+    <t>Este gráfico apresenta os vendedores com a maior proporção de pedidos entregues fora do prazo. Ele permite identificar quais sellers apresentam os piores níveis de confiabilidade em relação ao cumprimento de prazos. O fato de todos os vendedores do ranking apresentarem taxa máxima de atraso evidencia a existência de casos críticos de falha operacional que precisam ser priorizados pela gestão logística.</t>
+  </si>
+  <si>
+    <t>Este gráfico mostra os vendedores cujos pedidos apresentam os maiores atrasos médios em dias. Diferente da taxa de atraso, aqui é possível entender a gravidade do atraso em termos de tempo. Sellers com atrasos médios elevados indicam ineficiência operacional mais severa, impactando diretamente a experiência do cliente e a reputação da plataforma.</t>
+  </si>
+  <si>
     <t>Impacto do Atraso na Satisfação dos Clientes</t>
   </si>
   <si>
     <t>Comparação entre pedidos com e sem atraso com base no score médio e na probabilidade de nota mínima</t>
   </si>
   <si>
+    <t>Este gráfico compara a nota média dada pelos clientes quando o pedido é entregue no prazo versus quando há atraso. Ele evidencia de forma direta o impacto negativo do atraso na experiência do cliente. A diferença entre as médias demonstra que o atraso reduz significativamente a avaliação do serviço, afetando a percepção de qualidade da operação.</t>
+  </si>
+  <si>
+    <t>Este gráfico mostra a chance do cliente atribuir a pior nota possível (nota 1) em pedidos atrasados e não atrasados. Ele evidencia que a probabilidade de uma avaliação extremamente negativa é substancialmente maior quando ocorre atraso, reforçando que o atraso é um fator crítico de insatisfação extrema.</t>
+  </si>
+  <si>
     <t>Dashboard Geográfico — Atrasos por Estado | Olist</t>
   </si>
   <si>
     <t>Distribuição dos atrasos médios e volume de pedidos por UF</t>
+  </si>
+  <si>
+    <t>Este gráfico apresenta a proporção de pedidos que chegam fora do prazo em cada estado. Ele permite identificar onde o problema do atraso é mais frequente, mesmo que o atraso médio em dias não seja tão elevado. Estados com maior percentual indicam maior instabilidade na operação de entregas.</t>
+  </si>
+  <si>
+    <t>Este gráfico mostra quantos dias, em média, os pedidos chegam atrasados em cada estado. Ele permite identificar onde o atraso é mais grave quando ocorre, independentemente da quantidade de pedidos. Estados com valores mais altos indicam maior impacto logístico, pois os clientes ficam mais tempo além do prazo esperado.</t>
   </si>
 </sst>
 </file>
@@ -11212,7 +11230,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11341,6 +11359,12 @@
       <b/>
       <sz val="20"/>
       <color theme="3"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -11629,7 +11653,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -11687,6 +11711,35 @@
     <xf numFmtId="165" fontId="18" fillId="11" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11705,30 +11758,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -12211,6 +12283,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sellers!$K$2:$K$11</c:f>
@@ -13443,6 +13572,49 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Estados!$A$31:$A$40</c:f>
@@ -13485,7 +13657,7 @@
             <c:numRef>
               <c:f>Estados!$D$31:$D$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0.23</c:v>
@@ -13917,6 +14089,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Estados!$A$43:$A$52</c:f>
@@ -71883,7 +72112,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gbbKOjuoRZeEVqdD3kG3ADURwNwDabKfGmXZ7xYMVrL0BYHVJDZee8W3vsGQCFI1HlDd0dSIzzZk9LFz+RB5Ow==" saltValue="0M0dpGOJeBg8HUi/kerBQw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1Wyw1pMYnL43IZe6J20EpFQ6m9NUoUUTpdS2VYMiuHiT6l6kMWxPSJGCbANqaTQ21kDjOgHP3pTV1HwqmyTpiw==" saltValue="E9gFfPsqDBb4ckkfqTPNFA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
@@ -72593,7 +72822,7 @@
       <c r="A31" s="14" t="s">
         <v>3660</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="41">
         <v>0.23</v>
       </c>
     </row>
@@ -72601,7 +72830,7 @@
       <c r="A32" s="15" t="s">
         <v>3662</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="42">
         <v>0.19</v>
       </c>
     </row>
@@ -72609,7 +72838,7 @@
       <c r="A33" s="14" t="s">
         <v>3664</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="41">
         <v>0.15</v>
       </c>
     </row>
@@ -72617,7 +72846,7 @@
       <c r="A34" s="15" t="s">
         <v>3666</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="42">
         <v>0.15</v>
       </c>
     </row>
@@ -72625,7 +72854,7 @@
       <c r="A35" s="14" t="s">
         <v>3668</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="41">
         <v>0.14000000000000001</v>
       </c>
     </row>
@@ -72633,7 +72862,7 @@
       <c r="A36" s="15" t="s">
         <v>3670</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="42">
         <v>0.13</v>
       </c>
     </row>
@@ -72641,7 +72870,7 @@
       <c r="A37" s="14" t="s">
         <v>3672</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="41">
         <v>0.12</v>
       </c>
     </row>
@@ -72649,7 +72878,7 @@
       <c r="A38" s="15" t="s">
         <v>3674</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="42">
         <v>0.12</v>
       </c>
     </row>
@@ -72657,7 +72886,7 @@
       <c r="A39" s="14" t="s">
         <v>3676</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="41">
         <v>0.12</v>
       </c>
     </row>
@@ -72665,7 +72894,7 @@
       <c r="A40" s="15" t="s">
         <v>3678</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="42">
         <v>0.11</v>
       </c>
     </row>
@@ -72768,7 +72997,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -72785,34 +73014,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="26.25" customHeight="1">
       <c r="A1" s="5"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="44" t="s">
         <v>3713</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="53"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="47" t="s">
         <v>3714</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="50"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="49"/>
     </row>
     <row r="3" spans="1:10" ht="9.75" customHeight="1">
-      <c r="B3" s="41"/>
-      <c r="J3" s="49"/>
+      <c r="B3" s="35"/>
+      <c r="J3" s="40"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1">
       <c r="B4" s="29" t="s">
@@ -72867,35 +73096,26 @@
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="B7" s="41"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="35"/>
+      <c r="J7" s="40"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="41"/>
-      <c r="J8" s="49"/>
+      <c r="B8" s="35"/>
+      <c r="J8" s="40"/>
     </row>
     <row r="9" spans="1:10" ht="28.9">
-      <c r="B9" s="46"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="48"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="39"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="B11" s="45"/>
       <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="4vtp+bui6f1f86knTyPL2sRPm0DBABt7qHjLIoWM+8WoGKWngEKO+kkSSzv6VEc5R3kvpodUe8Hh7fAhQNyjYg==" saltValue="E2ITb6d9IiCOqYiz5y0UZA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
@@ -72948,7 +73168,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FAC38A-AFF4-40E9-B74F-401286B4933D}">
-  <dimension ref="B1:W19"/>
+  <dimension ref="B1:W27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="2:23" ht="23.25" customHeight="1">
@@ -72958,24 +73178,24 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="50" t="s">
         <v>3715</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
     </row>
     <row r="2" spans="2:23">
       <c r="B2" s="23"/>
@@ -72984,42 +73204,42 @@
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="51" t="s">
         <v>3716</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
     </row>
     <row r="3" spans="2:23">
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="40"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="55"/>
     </row>
     <row r="4" spans="2:23">
       <c r="H4" s="24"/>
@@ -73099,15 +73319,152 @@
       <c r="V19" s="27"/>
       <c r="W19" s="28"/>
     </row>
+    <row r="20" spans="8:23">
+      <c r="H20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="W20" s="25"/>
+    </row>
+    <row r="21" spans="8:23">
+      <c r="H21" s="59" t="s">
+        <v>3717</v>
+      </c>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="59" t="s">
+        <v>3718</v>
+      </c>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="64"/>
+      <c r="S21" s="64"/>
+      <c r="T21" s="64"/>
+      <c r="U21" s="64"/>
+      <c r="V21" s="64"/>
+      <c r="W21" s="65"/>
+    </row>
+    <row r="22" spans="8:23">
+      <c r="H22" s="66"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="68"/>
+    </row>
+    <row r="23" spans="8:23">
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="68"/>
+    </row>
+    <row r="24" spans="8:23">
+      <c r="H24" s="66"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="68"/>
+    </row>
+    <row r="25" spans="8:23">
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="68"/>
+    </row>
+    <row r="26" spans="8:23">
+      <c r="H26" s="66"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="68"/>
+    </row>
+    <row r="27" spans="8:23">
+      <c r="H27" s="69"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="70"/>
+      <c r="R27" s="70"/>
+      <c r="S27" s="70"/>
+      <c r="T27" s="70"/>
+      <c r="U27" s="70"/>
+      <c r="V27" s="70"/>
+      <c r="W27" s="71"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VCPtF4FrM/Ejplp3LNd+siXKX20aoTO7GEbEe8NkGKXT7Ij1pkI4v30Tt1/1h6XQuL4Ti0UVff60y9DYSkKMJg==" saltValue="305GNjH3ybjYYfbSsfU8Kw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OSOHBQcxmZqJKsnjvpfzGKK3R3IkZifmT1/YW/Z8/dc8ZdR0YD5sudNGxNjU2LW9sLcMEw4y/P0yaHqZIS1vTg==" saltValue="QfdRnP15WXQbZbj8vS0t2A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="H1:W19" name="Range1"/>
   </protectedRanges>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="H1:W1"/>
     <mergeCell ref="H2:W2"/>
     <mergeCell ref="H3:W3"/>
+    <mergeCell ref="H21:O27"/>
+    <mergeCell ref="P21:W27"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -73116,7 +73473,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6868A18-1963-4772-98DC-9002AA215FDE}">
-  <dimension ref="B1:W19"/>
+  <dimension ref="B1:W28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="2:23" ht="23.25" customHeight="1">
@@ -73126,24 +73483,24 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
-      <c r="H1" s="35" t="s">
-        <v>3717</v>
-      </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
+      <c r="H1" s="50" t="s">
+        <v>3719</v>
+      </c>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
     </row>
     <row r="2" spans="2:23">
       <c r="B2" s="23"/>
@@ -73152,42 +73509,42 @@
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="36" t="s">
-        <v>3718</v>
-      </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
+      <c r="H2" s="51" t="s">
+        <v>3720</v>
+      </c>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
     </row>
     <row r="3" spans="2:23">
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="40"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="55"/>
     </row>
     <row r="4" spans="2:23">
       <c r="H4" s="24"/>
@@ -73267,15 +73624,170 @@
       <c r="V19" s="27"/>
       <c r="W19" s="28"/>
     </row>
+    <row r="20" spans="8:23">
+      <c r="H20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="W20" s="25"/>
+    </row>
+    <row r="21" spans="8:23" ht="15" customHeight="1">
+      <c r="H21" s="59" t="s">
+        <v>3721</v>
+      </c>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="59" t="s">
+        <v>3722</v>
+      </c>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="64"/>
+      <c r="S21" s="64"/>
+      <c r="T21" s="64"/>
+      <c r="U21" s="64"/>
+      <c r="V21" s="64"/>
+      <c r="W21" s="65"/>
+    </row>
+    <row r="22" spans="8:23">
+      <c r="H22" s="66"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="68"/>
+    </row>
+    <row r="23" spans="8:23">
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="68"/>
+    </row>
+    <row r="24" spans="8:23">
+      <c r="H24" s="66"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="68"/>
+    </row>
+    <row r="25" spans="8:23">
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="68"/>
+    </row>
+    <row r="26" spans="8:23">
+      <c r="H26" s="66"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="68"/>
+    </row>
+    <row r="27" spans="8:23">
+      <c r="H27" s="66"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="67"/>
+      <c r="L27" s="67"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="66"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="68"/>
+    </row>
+    <row r="28" spans="8:23">
+      <c r="H28" s="69"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="70"/>
+      <c r="R28" s="70"/>
+      <c r="S28" s="70"/>
+      <c r="T28" s="70"/>
+      <c r="U28" s="70"/>
+      <c r="V28" s="70"/>
+      <c r="W28" s="71"/>
+    </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="iZxvKalKY9jRy6pJUqvdSeT9nfp1Wh7eGTJYkdsyrns6243HvLOaJUjHsqIWKDIgSKUcodX6AeylHukoIgiw6A==" saltValue="m8KMplTe487m37UlZ7G1FQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="H1:W19" name="Range1"/>
   </protectedRanges>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="H1:W1"/>
     <mergeCell ref="H2:W2"/>
     <mergeCell ref="H3:W3"/>
+    <mergeCell ref="H21:O28"/>
+    <mergeCell ref="P21:W28"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -73284,7 +73796,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B1:W19"/>
+  <dimension ref="B1:W29"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
     <row r="1" spans="2:23" ht="23.25" customHeight="1">
@@ -73294,24 +73806,24 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
-      <c r="H1" s="35" t="s">
-        <v>3719</v>
-      </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
+      <c r="H1" s="50" t="s">
+        <v>3723</v>
+      </c>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="50"/>
+      <c r="W1" s="50"/>
     </row>
     <row r="2" spans="2:23" ht="15">
       <c r="B2" s="23"/>
@@ -73320,42 +73832,42 @@
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="37" t="s">
-        <v>3720</v>
-      </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
+      <c r="H2" s="52" t="s">
+        <v>3724</v>
+      </c>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
     </row>
     <row r="3" spans="2:23" ht="15">
-      <c r="H3" s="38"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="40"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="55"/>
     </row>
     <row r="4" spans="2:23" ht="15">
       <c r="H4" s="24"/>
@@ -73424,8 +73936,8 @@
       <c r="K19" s="27"/>
       <c r="L19" s="27"/>
       <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="56"/>
       <c r="P19" s="27"/>
       <c r="Q19" s="27"/>
       <c r="R19" s="27"/>
@@ -73435,15 +73947,165 @@
       <c r="V19" s="27"/>
       <c r="W19" s="28"/>
     </row>
+    <row r="20" spans="8:23" ht="15">
+      <c r="H20" s="24"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="24"/>
+      <c r="W20" s="25"/>
+    </row>
+    <row r="21" spans="8:23" ht="14.45" customHeight="1">
+      <c r="H21" s="59" t="s">
+        <v>3725</v>
+      </c>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="59" t="s">
+        <v>3726</v>
+      </c>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="64"/>
+      <c r="S21" s="64"/>
+      <c r="T21" s="64"/>
+      <c r="U21" s="64"/>
+      <c r="V21" s="64"/>
+      <c r="W21" s="65"/>
+    </row>
+    <row r="22" spans="8:23" ht="14.45" customHeight="1">
+      <c r="H22" s="61"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="68"/>
+    </row>
+    <row r="23" spans="8:23" ht="14.45" customHeight="1">
+      <c r="H23" s="61"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="68"/>
+    </row>
+    <row r="24" spans="8:23" ht="15">
+      <c r="H24" s="61"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="68"/>
+    </row>
+    <row r="25" spans="8:23" ht="14.45" customHeight="1">
+      <c r="H25" s="61"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="66"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="68"/>
+    </row>
+    <row r="26" spans="8:23" ht="14.45" customHeight="1">
+      <c r="H26" s="61"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="66"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="68"/>
+    </row>
+    <row r="27" spans="8:23" ht="14.45" customHeight="1">
+      <c r="H27" s="62"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="70"/>
+      <c r="R27" s="70"/>
+      <c r="S27" s="70"/>
+      <c r="T27" s="70"/>
+      <c r="U27" s="70"/>
+      <c r="V27" s="70"/>
+      <c r="W27" s="71"/>
+    </row>
+    <row r="28" spans="8:23" ht="15">
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="43"/>
+      <c r="M28" s="43"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="43"/>
+    </row>
+    <row r="29" spans="8:23" ht="15"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="omvUILNx2OuRltYAaamMBcmEIL++VtxUE4s9T9DAw1x88m/PGt98qflBKJsGDm7CDzUHBDu8Y8+ng1B3FzxKcw==" saltValue="xWlkf1cvsaTgYPnhnGNuYw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oOgQnYo6q7JPlQQ7+/wspfQGIMAYu4g30DRZEyrFoQBfi6/0JGeqKXXwXJY/45qJUl8qs0Jj8AnzRv8t/PJ05g==" saltValue="uzK/sFnhbx1TwXcUHfUy8Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="H1:W19" name="Range1"/>
   </protectedRanges>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="H1:W1"/>
     <mergeCell ref="H2:W2"/>
     <mergeCell ref="H3:W3"/>
+    <mergeCell ref="P21:W27"/>
+    <mergeCell ref="H21:O27"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
